--- a/Analysis/Sensitivity_alpha_sweep_qwen.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_qwen.xlsx
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.20684</v>
+        <v>0.2082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.22204</v>
+        <v>0.22412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.46976</v>
+        <v>0.46566</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7682</v>
+        <v>0.7805199999999999</v>
       </c>
       <c r="J3" t="n">
         <v>195</v>
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.0086</v>
+        <v>0.00928</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005700000000000001</v>
+        <v>0.005679999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29806</v>
+        <v>0.30014</v>
       </c>
       <c r="I5" t="n">
-        <v>0.68342</v>
+        <v>0.68138</v>
       </c>
       <c r="J5" t="n">
         <v>194.6</v>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.19316</v>
+        <v>0.19112</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2051</v>
+        <v>0.20562</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4513</v>
+        <v>0.45026</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7528</v>
+        <v>0.7702600000000001</v>
       </c>
       <c r="J6" t="n">
         <v>195</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.85612</v>
+        <v>0.8595200000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.87052</v>
+        <v>0.8730800000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8756600000000001</v>
+        <v>0.8808</v>
       </c>
       <c r="I7" t="n">
         <v>0.9681599999999999</v>
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.20342</v>
+        <v>0.20752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.21796</v>
+        <v>0.22202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46668</v>
+        <v>0.46258</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7630800000000001</v>
+        <v>0.7794800000000001</v>
       </c>
       <c r="J9" t="n">
         <v>195</v>
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.009980000000000001</v>
+        <v>0.007940000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007760000000000001</v>
+        <v>0.0062</v>
       </c>
       <c r="H11" t="n">
-        <v>0.30012</v>
+        <v>0.29704</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6772799999999999</v>
+        <v>0.67726</v>
       </c>
       <c r="J11" t="n">
         <v>194.6</v>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.20684</v>
+        <v>0.21024</v>
       </c>
       <c r="G12" t="n">
-        <v>0.22204</v>
+        <v>0.22614</v>
       </c>
       <c r="H12" t="n">
-        <v>0.46976</v>
+        <v>0.4676999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7682</v>
+        <v>0.7825599999999999</v>
       </c>
       <c r="J12" t="n">
         <v>195</v>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8801</v>
+        <v>0.87804</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8895199999999999</v>
+        <v>0.88852</v>
       </c>
       <c r="H13" t="n">
-        <v>0.89724</v>
+        <v>0.89416</v>
       </c>
       <c r="I13" t="n">
-        <v>0.96918</v>
+        <v>0.9702</v>
       </c>
       <c r="J13" t="n">
         <v>194.6</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.01476</v>
+        <v>0.01272</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01188</v>
+        <v>0.01032</v>
       </c>
       <c r="H14" t="n">
-        <v>0.30528</v>
+        <v>0.30218</v>
       </c>
       <c r="I14" t="n">
         <v>0.6782999999999999</v>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.213</v>
+        <v>0.21642</v>
       </c>
       <c r="G15" t="n">
-        <v>0.22768</v>
+        <v>0.23178</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4718</v>
+        <v>0.4697600000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.76718</v>
+        <v>0.78154</v>
       </c>
       <c r="J15" t="n">
         <v>195</v>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.87532</v>
+        <v>0.8732599999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8875</v>
+        <v>0.8864600000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8941799999999999</v>
+        <v>0.8911</v>
       </c>
       <c r="I16" t="n">
-        <v>0.96918</v>
+        <v>0.9702</v>
       </c>
       <c r="J16" t="n">
         <v>194.6</v>
